--- a/Framework_MWC_Testing/data/TestData.xlsx
+++ b/Framework_MWC_Testing/data/TestData.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Search" sheetId="3" r:id="rId3"/>
     <sheet name="Profile" sheetId="4" r:id="rId4"/>
     <sheet name="Order" sheetId="5" r:id="rId5"/>
+    <sheet name="Product_Review" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -1819,4 +1820,409 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Testcase</v>
+      </c>
+      <c r="B1" t="str">
+        <v>FullName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Content</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Expected</v>
+      </c>
+      <c r="L1" t="str">
+        <v/>
+      </c>
+      <c r="M1" t="str">
+        <v/>
+      </c>
+      <c r="N1" t="str">
+        <v/>
+      </c>
+      <c r="O1" t="str">
+        <v/>
+      </c>
+      <c r="P1" t="str">
+        <v/>
+      </c>
+      <c r="Q1" t="str">
+        <v/>
+      </c>
+      <c r="R1" t="str">
+        <v/>
+      </c>
+      <c r="S1" t="str">
+        <v/>
+      </c>
+      <c r="T1" t="str">
+        <v/>
+      </c>
+      <c r="U1" t="str">
+        <v/>
+      </c>
+      <c r="V1" t="str">
+        <v/>
+      </c>
+      <c r="W1" t="str">
+        <v/>
+      </c>
+      <c r="X1" t="str">
+        <v/>
+      </c>
+      <c r="Y1" t="str">
+        <v/>
+      </c>
+      <c r="Z1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DG1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D2" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F2" t="str">
+        <v>4</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Gửi bình luận thành công!</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DG2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D3" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F3" t="str">
+        <v>5</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Vui lòng nhập!</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DG3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="D4" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F4" t="str">
+        <v>3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Vui lòng nhập!</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DG4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Vui lòng nhập!</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DG5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D6" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Vui lòng nhập!</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DG6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C7" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D7" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Vui lòng nhập!</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DG7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C8" t="str">
+        <v>03</v>
+      </c>
+      <c r="D8" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F8" t="str">
+        <v>5</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Số điện thoại không hợp lệ</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DG8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C9" t="str">
+        <v>abdc</v>
+      </c>
+      <c r="D9" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F9" t="str">
+        <v>4</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Số điện thoại không hợp lệ</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DG9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C10" t="str">
+        <v>!@#$%</v>
+      </c>
+      <c r="D10" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F10" t="str">
+        <v>5</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Số điện thoại không hợp lệ</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>DG10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C11" t="str">
+        <v>032145678999</v>
+      </c>
+      <c r="D11" t="str">
+        <v>anhduong@gmail.com</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F11" t="str">
+        <v>4</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Số điện thoại không hợp lệ</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>DG11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C12" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D12" t="str">
+        <v>anh1@_x000d_</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F12" t="str">
+        <v>4</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Email không đúng định dạng</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>DG12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C13" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D13" t="str">
+        <v>anh1@@_x000d_</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Email không đúng định dạng</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>DG13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Ánh Dương Phạm</v>
+      </c>
+      <c r="C14" t="str">
+        <v>0321456789</v>
+      </c>
+      <c r="D14" t="str">
+        <v>anh1@gmail._x000d_</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Giày xinh</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Giày rất đẹp, vừa form chân, y như hình</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Email không đúng định dạng</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z14"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/Framework_MWC_Testing/data/TestData.xlsx
+++ b/Framework_MWC_Testing/data/TestData.xlsx
@@ -554,7 +554,7 @@
         <v>DK1</v>
       </c>
       <c r="B2" t="str">
-        <v>Phạm Ánh Ngọc Lan</v>
+        <v>Phạm Thanh An</v>
       </c>
       <c r="C2" t="str">
         <v>0359694333</v>
@@ -566,7 +566,7 @@
         <v>Abcde12345</v>
       </c>
       <c r="F2" t="str">
-        <v>Phạm Ánh Ngọc Lan</v>
+        <v>Phạm Thanh An</v>
       </c>
     </row>
     <row r="3">
